--- a/MAU_02_Template.xlsx
+++ b/MAU_02_Template.xlsx
@@ -297,7 +297,7 @@
     <t>Chuỗi</t>
   </si>
   <si>
-    <t>Mã khoa/phòng nơi nhân viên công tác (tham chiếu MAU_01)</t>
+    <t>Mã khoa theo quy định: Khám bệnh tại Khoa khám bệnh ghi mã bàn khám; Làm việc tại khoa lâm sàng/cận lâm sàng/dinh dưỡng/dược/chống nhiễm khuẩn ghi mã khoa; Nhiều khoa ghi lần lượt mã từng khoa cách nhau bằng ";", mã đầu tiên là khoa quản lý; Khám luân phiên ghi mã khoa + ";", + mã bàn khám; Khác (điều dưỡng, kỹ thuật...) tại Khoa khám bệnh ghi "K01"</t>
   </si>
   <si>
     <t>Tên khoa/phòng</t>
